--- a/results/job_matches_2026-06-07.xlsx
+++ b/results/job_matches_2026-06-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Data Architect</t>
+          <t>Database Engineer/Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trianz</t>
+          <t>ron turley associates</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Clinton, NJ, US USA</t>
+          <t>Glendale, AZ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4383b83bebf58ee2</t>
+          <t>https://www.indeed.com/viewjob?jk=38fb9ceb49a96b57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Database Engineer/Architect</t>
+          <t>Sr Confluent Kafka Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ron turley associates</t>
+          <t>NSV IT SOLUTIONS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Glendale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,242 +531,242 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38fb9ceb49a96b57</t>
+          <t>https://www.indeed.com/viewjob?jk=3731032ae0f7a545</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Confluent Kafka Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NSV IT SOLUTIONS</t>
+          <t>FocusKPI Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3731032ae0f7a545</t>
+          <t>https://www.indeed.com/viewjob?jk=fbdbfc37bf1ca190</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FocusKPI Inc.</t>
+          <t>ATVIO Biotech</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Hive, Spark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbdbfc37bf1ca190</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac69009cfd6f44c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Data Engineer- Data Platform &amp; AI Enablement</t>
+          <t>OpenText xECM Administrator</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c6ead6041dd8b2</t>
+          <t>https://www.indeed.com/viewjob?jk=789eced375518056</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Bricks Migration and Support engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f646314becd0f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=10e4d2d78aad0fb7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Bricks Migration and Support engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Cloud Storage, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6dc96e2f68af48</t>
+          <t>https://www.indeed.com/viewjob?jk=08dac6e8a6a35c88</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>New York Blood Center</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rye, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558c0c0c483e56c0</t>
+          <t>https://www.indeed.com/viewjob?jk=fd370855fc5dbc9a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OpenText xECM Administrator</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=789eced375518056</t>
+          <t>https://www.indeed.com/viewjob?jk=d784be9eb68c3d91</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Audacy, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415deca736697451</t>
+          <t>https://www.indeed.com/viewjob?jk=9da17c48b0c22ee4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c05afb61055331</t>
+          <t>https://www.indeed.com/viewjob?jk=49bd1e8c944ff980</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mustang Cat</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,497 +881,2457 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
+          <t>https://www.indeed.com/viewjob?jk=62cd9c61bbe2ba9a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Kafka Platform Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26482741958a217b</t>
+          <t>https://www.indeed.com/viewjob?jk=5e945058b2aeb81e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e406b4cb8e2231</t>
+          <t>https://www.indeed.com/viewjob?jk=71e2a2a565e81c13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II, BS Solutions</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2da1cdaefbd7649</t>
+          <t>https://www.indeed.com/viewjob?jk=e4c2922604286744</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Site Reliability Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088f92fa01dbe0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=0eda203594437eb0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4d5b6c0ea750fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c7da71f5c4c140fd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tyto Athene</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e23acbb45cb289</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e717cdb8e459ed</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5db37bdf41206f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=783563088e4850d3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist, Marketing Analytics &amp; Measurement</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1861d953a806a35d</t>
+          <t>https://www.indeed.com/viewjob?jk=caa727dc99a46aef</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Backend Java Engineer - Post Trade Accounting, Associate</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a70a6a9d580d712</t>
+          <t>https://www.indeed.com/viewjob?jk=8615c522efc71334</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Business Services Developer (Business Services Analyst)</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>County of Orange</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab95d16515240126</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6ae33243c395f5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data &amp; Digital Solutions Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02fdb552c664e0b2</t>
+          <t>https://www.indeed.com/viewjob?jk=b2caf8633eb99f5e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c495635e58d0e5</t>
+          <t>https://www.indeed.com/viewjob?jk=37c812e3f35b5835</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Distinguished Engineer, Data Platform</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ec3ffd343b6320</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef92fef0e7ac2af</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82611021e50403b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3964af1e193d6df3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57945f07d8dd1359</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=764072f6ce811075</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b3b589ca8a6e80f</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24650c3c8a602a7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03bea43e652f03fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bb4026df23eb97b</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c93475e7d040c153</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=456f8fa32939f19b</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99c05afb61055331</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Mustang Cat</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>Houston, TX, US USA</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="D38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior AI Data Architect</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Modine Manufacturing Company</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05d964f0d99760fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer II, BS Solutions</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Frontline Education</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a457b4897928b47</t>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2da1cdaefbd7649</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Casey's</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ankeny, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f4d5b6c0ea750fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Business Services Developer (Business Services Analyst)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>County of Orange</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab95d16515240126</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Data Scientist, Marketing Analytics &amp; Measurement</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Staples</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Framingham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1861d953a806a35d</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4c495635e58d0e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcfb9a55bfdcda15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c661fd3d1a35149</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3af5dbc4a7642e17</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a05cc00f3398fb9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4eb07a25aaeb4be3</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ddac65267477c40</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e425667f20dcb7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1873482056030d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab22c7230af34e68</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=677be9646b0e06df</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d5e09a480919567</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd1bd277622288c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42a71d4cd495130b</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a52685267df3f959</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fcc937a8b5e2489</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5ff1ae9ce8cebc9</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=caeae51b9c1b0f4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdd2ae13e28a4887</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06b3d09e86b123a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=036b19c06fa11eda</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c11d63f000f42ba2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60e096ff0af09e5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b043df0a94d01e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ebef8251dce5834</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59559b19a431de6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18319f312711ee31</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e807d665db859229</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98a283e17753436e</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5c04a5eeae8858a</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04a2f6320142a662</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba86b9b1e8a2c34b</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8109c00824ee19e</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0807f3685e925ebe</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abcd4343cd691b21</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc21abcfcbae5841</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c5172ad7fba06cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95ccbb7fea6307b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54ccb8a0b4e4366c</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Product Architect</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20da8d36ff151411</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-07.xlsx
+++ b/results/job_matches_2026-06-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,47 +538,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FocusKPI Inc.</t>
+          <t>ATVIO Biotech</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Hive, Spark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbdbfc37bf1ca190</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac69009cfd6f44c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>OpenText xECM Administrator</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ATVIO Biotech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac69009cfd6f44c</t>
+          <t>https://www.indeed.com/viewjob?jk=789eced375518056</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OpenText xECM Administrator</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=789eced375518056</t>
+          <t>https://www.indeed.com/viewjob?jk=10e4d2d78aad0fb7</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e4d2d78aad0fb7</t>
+          <t>https://www.indeed.com/viewjob?jk=08dac6e8a6a35c88</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08dac6e8a6a35c88</t>
+          <t>https://www.indeed.com/viewjob?jk=fd370855fc5dbc9a</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd370855fc5dbc9a</t>
+          <t>https://www.indeed.com/viewjob?jk=d784be9eb68c3d91</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d784be9eb68c3d91</t>
+          <t>https://www.indeed.com/viewjob?jk=9da17c48b0c22ee4</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da17c48b0c22ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=49bd1e8c944ff980</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49bd1e8c944ff980</t>
+          <t>https://www.indeed.com/viewjob?jk=62cd9c61bbe2ba9a</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62cd9c61bbe2ba9a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e945058b2aeb81e</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e945058b2aeb81e</t>
+          <t>https://www.indeed.com/viewjob?jk=71e2a2a565e81c13</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e2a2a565e81c13</t>
+          <t>https://www.indeed.com/viewjob?jk=e4c2922604286744</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4c2922604286744</t>
+          <t>https://www.indeed.com/viewjob?jk=0eda203594437eb0</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eda203594437eb0</t>
+          <t>https://www.indeed.com/viewjob?jk=c7da71f5c4c140fd</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7da71f5c4c140fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e717cdb8e459ed</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e717cdb8e459ed</t>
+          <t>https://www.indeed.com/viewjob?jk=783563088e4850d3</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783563088e4850d3</t>
+          <t>https://www.indeed.com/viewjob?jk=caa727dc99a46aef</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa727dc99a46aef</t>
+          <t>https://www.indeed.com/viewjob?jk=8615c522efc71334</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8615c522efc71334</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6ae33243c395f5</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6ae33243c395f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b2caf8633eb99f5e</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2caf8633eb99f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=37c812e3f35b5835</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37c812e3f35b5835</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef92fef0e7ac2af</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef92fef0e7ac2af</t>
+          <t>https://www.indeed.com/viewjob?jk=82611021e50403b1</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82611021e50403b1</t>
+          <t>https://www.indeed.com/viewjob?jk=3964af1e193d6df3</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3964af1e193d6df3</t>
+          <t>https://www.indeed.com/viewjob?jk=57945f07d8dd1359</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57945f07d8dd1359</t>
+          <t>https://www.indeed.com/viewjob?jk=764072f6ce811075</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=764072f6ce811075</t>
+          <t>https://www.indeed.com/viewjob?jk=1b3b589ca8a6e80f</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b3b589ca8a6e80f</t>
+          <t>https://www.indeed.com/viewjob?jk=24650c3c8a602a7e</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24650c3c8a602a7e</t>
+          <t>https://www.indeed.com/viewjob?jk=03bea43e652f03fd</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03bea43e652f03fd</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb4026df23eb97b</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb4026df23eb97b</t>
+          <t>https://www.indeed.com/viewjob?jk=c93475e7d040c153</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93475e7d040c153</t>
+          <t>https://www.indeed.com/viewjob?jk=456f8fa32939f19b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=456f8fa32939f19b</t>
+          <t>https://www.indeed.com/viewjob?jk=99c05afb61055331</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mustang Cat</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c05afb61055331</t>
+          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mustang Cat</t>
+          <t>Modine Manufacturing Company</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
+          <t>https://www.indeed.com/viewjob?jk=05d964f0d99760fd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AI Data Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Modine Manufacturing Company</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,174 +1781,174 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d964f0d99760fd</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1fdc7b0acc6f95</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II, BS Solutions</t>
+          <t>Business Services Developer (Business Services Analyst)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>County of Orange</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2da1cdaefbd7649</t>
+          <t>https://www.indeed.com/viewjob?jk=ab95d16515240126</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Scientist, Marketing Analytics &amp; Measurement</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Framingham, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4d5b6c0ea750fd</t>
+          <t>https://www.indeed.com/viewjob?jk=1861d953a806a35d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Business Services Developer (Business Services Analyst)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>County of Orange</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, GCP, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab95d16515240126</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c495635e58d0e5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Scientist, Marketing Analytics &amp; Measurement</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1861d953a806a35d</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfb9a55bfdcda15</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c495635e58d0e5</t>
+          <t>https://www.indeed.com/viewjob?jk=1c661fd3d1a35149</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfb9a55bfdcda15</t>
+          <t>https://www.indeed.com/viewjob?jk=3af5dbc4a7642e17</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c661fd3d1a35149</t>
+          <t>https://www.indeed.com/viewjob?jk=a05cc00f3398fb9e</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af5dbc4a7642e17</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb07a25aaeb4be3</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05cc00f3398fb9e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ddac65267477c40</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb07a25aaeb4be3</t>
+          <t>https://www.indeed.com/viewjob?jk=2e425667f20dcb7e</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ddac65267477c40</t>
+          <t>https://www.indeed.com/viewjob?jk=b1873482056030d0</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e425667f20dcb7e</t>
+          <t>https://www.indeed.com/viewjob?jk=ab22c7230af34e68</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1873482056030d0</t>
+          <t>https://www.indeed.com/viewjob?jk=677be9646b0e06df</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab22c7230af34e68</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5e09a480919567</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677be9646b0e06df</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1bd277622288c0</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5e09a480919567</t>
+          <t>https://www.indeed.com/viewjob?jk=42a71d4cd495130b</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1bd277622288c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a52685267df3f959</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42a71d4cd495130b</t>
+          <t>https://www.indeed.com/viewjob?jk=8fcc937a8b5e2489</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a52685267df3f959</t>
+          <t>https://www.indeed.com/viewjob?jk=d5ff1ae9ce8cebc9</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fcc937a8b5e2489</t>
+          <t>https://www.indeed.com/viewjob?jk=caeae51b9c1b0f4a</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5ff1ae9ce8cebc9</t>
+          <t>https://www.indeed.com/viewjob?jk=cdd2ae13e28a4887</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caeae51b9c1b0f4a</t>
+          <t>https://www.indeed.com/viewjob?jk=06b3d09e86b123a8</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdd2ae13e28a4887</t>
+          <t>https://www.indeed.com/viewjob?jk=036b19c06fa11eda</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b3d09e86b123a8</t>
+          <t>https://www.indeed.com/viewjob?jk=c11d63f000f42ba2</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=036b19c06fa11eda</t>
+          <t>https://www.indeed.com/viewjob?jk=60e096ff0af09e5a</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11d63f000f42ba2</t>
+          <t>https://www.indeed.com/viewjob?jk=5b043df0a94d01e0</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e096ff0af09e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=4ebef8251dce5834</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b043df0a94d01e0</t>
+          <t>https://www.indeed.com/viewjob?jk=59559b19a431de6c</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ebef8251dce5834</t>
+          <t>https://www.indeed.com/viewjob?jk=18319f312711ee31</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59559b19a431de6c</t>
+          <t>https://www.indeed.com/viewjob?jk=e807d665db859229</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18319f312711ee31</t>
+          <t>https://www.indeed.com/viewjob?jk=98a283e17753436e</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e807d665db859229</t>
+          <t>https://www.indeed.com/viewjob?jk=f5c04a5eeae8858a</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a283e17753436e</t>
+          <t>https://www.indeed.com/viewjob?jk=04a2f6320142a662</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5c04a5eeae8858a</t>
+          <t>https://www.indeed.com/viewjob?jk=ba86b9b1e8a2c34b</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a2f6320142a662</t>
+          <t>https://www.indeed.com/viewjob?jk=b8109c00824ee19e</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba86b9b1e8a2c34b</t>
+          <t>https://www.indeed.com/viewjob?jk=0807f3685e925ebe</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8109c00824ee19e</t>
+          <t>https://www.indeed.com/viewjob?jk=abcd4343cd691b21</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0807f3685e925ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=bc21abcfcbae5841</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abcd4343cd691b21</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5172ad7fba06cf</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc21abcfcbae5841</t>
+          <t>https://www.indeed.com/viewjob?jk=95ccbb7fea6307b3</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5172ad7fba06cf</t>
+          <t>https://www.indeed.com/viewjob?jk=54ccb8a0b4e4366c</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3260,76 +3260,6 @@
         </is>
       </c>
       <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95ccbb7fea6307b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54ccb8a0b4e4366c</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=20da8d36ff151411</t>
         </is>

--- a/results/job_matches_2026-06-07.xlsx
+++ b/results/job_matches_2026-06-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Database Engineer/Architect</t>
+          <t>Sr Confluent Kafka Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ron turley associates</t>
+          <t>NSV IT SOLUTIONS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Glendale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38fb9ceb49a96b57</t>
+          <t>https://www.indeed.com/viewjob?jk=3731032ae0f7a545</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Confluent Kafka Architect</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NSV IT SOLUTIONS</t>
+          <t>ATVIO Biotech</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3731032ae0f7a545</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac69009cfd6f44c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>OpenText xECM Administrator</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ATVIO Biotech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac69009cfd6f44c</t>
+          <t>https://www.indeed.com/viewjob?jk=789eced375518056</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OpenText xECM Administrator</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=789eced375518056</t>
+          <t>https://www.indeed.com/viewjob?jk=10e4d2d78aad0fb7</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e4d2d78aad0fb7</t>
+          <t>https://www.indeed.com/viewjob?jk=08dac6e8a6a35c88</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08dac6e8a6a35c88</t>
+          <t>https://www.indeed.com/viewjob?jk=fd370855fc5dbc9a</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd370855fc5dbc9a</t>
+          <t>https://www.indeed.com/viewjob?jk=d784be9eb68c3d91</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d784be9eb68c3d91</t>
+          <t>https://www.indeed.com/viewjob?jk=9da17c48b0c22ee4</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da17c48b0c22ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=49bd1e8c944ff980</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49bd1e8c944ff980</t>
+          <t>https://www.indeed.com/viewjob?jk=62cd9c61bbe2ba9a</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62cd9c61bbe2ba9a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e945058b2aeb81e</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e945058b2aeb81e</t>
+          <t>https://www.indeed.com/viewjob?jk=71e2a2a565e81c13</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e2a2a565e81c13</t>
+          <t>https://www.indeed.com/viewjob?jk=e4c2922604286744</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4c2922604286744</t>
+          <t>https://www.indeed.com/viewjob?jk=0eda203594437eb0</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eda203594437eb0</t>
+          <t>https://www.indeed.com/viewjob?jk=c7da71f5c4c140fd</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7da71f5c4c140fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e717cdb8e459ed</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e717cdb8e459ed</t>
+          <t>https://www.indeed.com/viewjob?jk=783563088e4850d3</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783563088e4850d3</t>
+          <t>https://www.indeed.com/viewjob?jk=caa727dc99a46aef</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa727dc99a46aef</t>
+          <t>https://www.indeed.com/viewjob?jk=8615c522efc71334</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8615c522efc71334</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6ae33243c395f5</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6ae33243c395f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b2caf8633eb99f5e</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2caf8633eb99f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=37c812e3f35b5835</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37c812e3f35b5835</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef92fef0e7ac2af</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef92fef0e7ac2af</t>
+          <t>https://www.indeed.com/viewjob?jk=82611021e50403b1</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82611021e50403b1</t>
+          <t>https://www.indeed.com/viewjob?jk=3964af1e193d6df3</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3964af1e193d6df3</t>
+          <t>https://www.indeed.com/viewjob?jk=57945f07d8dd1359</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57945f07d8dd1359</t>
+          <t>https://www.indeed.com/viewjob?jk=764072f6ce811075</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=764072f6ce811075</t>
+          <t>https://www.indeed.com/viewjob?jk=1b3b589ca8a6e80f</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b3b589ca8a6e80f</t>
+          <t>https://www.indeed.com/viewjob?jk=24650c3c8a602a7e</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24650c3c8a602a7e</t>
+          <t>https://www.indeed.com/viewjob?jk=03bea43e652f03fd</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03bea43e652f03fd</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb4026df23eb97b</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb4026df23eb97b</t>
+          <t>https://www.indeed.com/viewjob?jk=c93475e7d040c153</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93475e7d040c153</t>
+          <t>https://www.indeed.com/viewjob?jk=456f8fa32939f19b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=456f8fa32939f19b</t>
+          <t>https://www.indeed.com/viewjob?jk=99c05afb61055331</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior AI Data Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Modine Manufacturing Company</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,199 +1686,199 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c05afb61055331</t>
+          <t>https://www.indeed.com/viewjob?jk=05d964f0d99760fd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mustang Cat</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Fact Tables, ETL</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f8c84cd358c94d</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1fdc7b0acc6f95</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior AI Data Architect</t>
+          <t>Business Services Developer (Business Services Analyst)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Modine Manufacturing Company</t>
+          <t>County of Orange</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d964f0d99760fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ab95d16515240126</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Azure, GCP, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1fdc7b0acc6f95</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c495635e58d0e5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Business Services Developer (Business Services Analyst)</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>County of Orange</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab95d16515240126</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfb9a55bfdcda15</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Scientist, Marketing Analytics &amp; Measurement</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, MLOps, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1861d953a806a35d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c661fd3d1a35149</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c495635e58d0e5</t>
+          <t>https://www.indeed.com/viewjob?jk=3af5dbc4a7642e17</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfb9a55bfdcda15</t>
+          <t>https://www.indeed.com/viewjob?jk=a05cc00f3398fb9e</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c661fd3d1a35149</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb07a25aaeb4be3</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af5dbc4a7642e17</t>
+          <t>https://www.indeed.com/viewjob?jk=2ddac65267477c40</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05cc00f3398fb9e</t>
+          <t>https://www.indeed.com/viewjob?jk=2e425667f20dcb7e</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb07a25aaeb4be3</t>
+          <t>https://www.indeed.com/viewjob?jk=b1873482056030d0</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ddac65267477c40</t>
+          <t>https://www.indeed.com/viewjob?jk=ab22c7230af34e68</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e425667f20dcb7e</t>
+          <t>https://www.indeed.com/viewjob?jk=677be9646b0e06df</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1873482056030d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5e09a480919567</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab22c7230af34e68</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1bd277622288c0</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677be9646b0e06df</t>
+          <t>https://www.indeed.com/viewjob?jk=42a71d4cd495130b</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5e09a480919567</t>
+          <t>https://www.indeed.com/viewjob?jk=a52685267df3f959</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1bd277622288c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8fcc937a8b5e2489</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42a71d4cd495130b</t>
+          <t>https://www.indeed.com/viewjob?jk=d5ff1ae9ce8cebc9</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a52685267df3f959</t>
+          <t>https://www.indeed.com/viewjob?jk=caeae51b9c1b0f4a</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fcc937a8b5e2489</t>
+          <t>https://www.indeed.com/viewjob?jk=cdd2ae13e28a4887</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5ff1ae9ce8cebc9</t>
+          <t>https://www.indeed.com/viewjob?jk=06b3d09e86b123a8</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caeae51b9c1b0f4a</t>
+          <t>https://www.indeed.com/viewjob?jk=036b19c06fa11eda</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdd2ae13e28a4887</t>
+          <t>https://www.indeed.com/viewjob?jk=c11d63f000f42ba2</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b3d09e86b123a8</t>
+          <t>https://www.indeed.com/viewjob?jk=60e096ff0af09e5a</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=036b19c06fa11eda</t>
+          <t>https://www.indeed.com/viewjob?jk=5b043df0a94d01e0</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11d63f000f42ba2</t>
+          <t>https://www.indeed.com/viewjob?jk=4ebef8251dce5834</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e096ff0af09e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=59559b19a431de6c</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b043df0a94d01e0</t>
+          <t>https://www.indeed.com/viewjob?jk=18319f312711ee31</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ebef8251dce5834</t>
+          <t>https://www.indeed.com/viewjob?jk=e807d665db859229</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59559b19a431de6c</t>
+          <t>https://www.indeed.com/viewjob?jk=98a283e17753436e</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18319f312711ee31</t>
+          <t>https://www.indeed.com/viewjob?jk=f5c04a5eeae8858a</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e807d665db859229</t>
+          <t>https://www.indeed.com/viewjob?jk=04a2f6320142a662</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a283e17753436e</t>
+          <t>https://www.indeed.com/viewjob?jk=ba86b9b1e8a2c34b</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5c04a5eeae8858a</t>
+          <t>https://www.indeed.com/viewjob?jk=b8109c00824ee19e</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a2f6320142a662</t>
+          <t>https://www.indeed.com/viewjob?jk=0807f3685e925ebe</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba86b9b1e8a2c34b</t>
+          <t>https://www.indeed.com/viewjob?jk=abcd4343cd691b21</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8109c00824ee19e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc21abcfcbae5841</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0807f3685e925ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5172ad7fba06cf</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abcd4343cd691b21</t>
+          <t>https://www.indeed.com/viewjob?jk=95ccbb7fea6307b3</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc21abcfcbae5841</t>
+          <t>https://www.indeed.com/viewjob?jk=54ccb8a0b4e4366c</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3155,111 +3155,6 @@
         </is>
       </c>
       <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5172ad7fba06cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95ccbb7fea6307b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54ccb8a0b4e4366c</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=20da8d36ff151411</t>
         </is>

--- a/results/job_matches_2026-06-07.xlsx
+++ b/results/job_matches_2026-06-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OpenText xECM Administrator</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=789eced375518056</t>
+          <t>https://www.indeed.com/viewjob?jk=10e4d2d78aad0fb7</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e4d2d78aad0fb7</t>
+          <t>https://www.indeed.com/viewjob?jk=08dac6e8a6a35c88</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08dac6e8a6a35c88</t>
+          <t>https://www.indeed.com/viewjob?jk=fd370855fc5dbc9a</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd370855fc5dbc9a</t>
+          <t>https://www.indeed.com/viewjob?jk=d784be9eb68c3d91</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d784be9eb68c3d91</t>
+          <t>https://www.indeed.com/viewjob?jk=9da17c48b0c22ee4</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da17c48b0c22ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=49bd1e8c944ff980</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49bd1e8c944ff980</t>
+          <t>https://www.indeed.com/viewjob?jk=62cd9c61bbe2ba9a</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62cd9c61bbe2ba9a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e945058b2aeb81e</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e945058b2aeb81e</t>
+          <t>https://www.indeed.com/viewjob?jk=71e2a2a565e81c13</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e2a2a565e81c13</t>
+          <t>https://www.indeed.com/viewjob?jk=e4c2922604286744</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4c2922604286744</t>
+          <t>https://www.indeed.com/viewjob?jk=0eda203594437eb0</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eda203594437eb0</t>
+          <t>https://www.indeed.com/viewjob?jk=c7da71f5c4c140fd</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7da71f5c4c140fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e717cdb8e459ed</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e717cdb8e459ed</t>
+          <t>https://www.indeed.com/viewjob?jk=783563088e4850d3</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783563088e4850d3</t>
+          <t>https://www.indeed.com/viewjob?jk=caa727dc99a46aef</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa727dc99a46aef</t>
+          <t>https://www.indeed.com/viewjob?jk=8615c522efc71334</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8615c522efc71334</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6ae33243c395f5</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6ae33243c395f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b2caf8633eb99f5e</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2caf8633eb99f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=37c812e3f35b5835</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37c812e3f35b5835</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef92fef0e7ac2af</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef92fef0e7ac2af</t>
+          <t>https://www.indeed.com/viewjob?jk=82611021e50403b1</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82611021e50403b1</t>
+          <t>https://www.indeed.com/viewjob?jk=3964af1e193d6df3</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3964af1e193d6df3</t>
+          <t>https://www.indeed.com/viewjob?jk=57945f07d8dd1359</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57945f07d8dd1359</t>
+          <t>https://www.indeed.com/viewjob?jk=764072f6ce811075</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=764072f6ce811075</t>
+          <t>https://www.indeed.com/viewjob?jk=1b3b589ca8a6e80f</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b3b589ca8a6e80f</t>
+          <t>https://www.indeed.com/viewjob?jk=24650c3c8a602a7e</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24650c3c8a602a7e</t>
+          <t>https://www.indeed.com/viewjob?jk=03bea43e652f03fd</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03bea43e652f03fd</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb4026df23eb97b</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb4026df23eb97b</t>
+          <t>https://www.indeed.com/viewjob?jk=c93475e7d040c153</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93475e7d040c153</t>
+          <t>https://www.indeed.com/viewjob?jk=456f8fa32939f19b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Senior AI Data Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Modine Manufacturing Company</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,164 +1616,164 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=456f8fa32939f19b</t>
+          <t>https://www.indeed.com/viewjob?jk=05d964f0d99760fd</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c05afb61055331</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1fdc7b0acc6f95</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior AI Data Architect</t>
+          <t>Business Services Developer (Business Services Analyst)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Modine Manufacturing Company</t>
+          <t>County of Orange</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d964f0d99760fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ab95d16515240126</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1fdc7b0acc6f95</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfb9a55bfdcda15</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Business Services Developer (Business Services Analyst)</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>County of Orange</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab95d16515240126</t>
+          <t>https://www.indeed.com/viewjob?jk=1c661fd3d1a35149</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c495635e58d0e5</t>
+          <t>https://www.indeed.com/viewjob?jk=3af5dbc4a7642e17</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfb9a55bfdcda15</t>
+          <t>https://www.indeed.com/viewjob?jk=a05cc00f3398fb9e</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c661fd3d1a35149</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb07a25aaeb4be3</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af5dbc4a7642e17</t>
+          <t>https://www.indeed.com/viewjob?jk=2ddac65267477c40</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05cc00f3398fb9e</t>
+          <t>https://www.indeed.com/viewjob?jk=2e425667f20dcb7e</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb07a25aaeb4be3</t>
+          <t>https://www.indeed.com/viewjob?jk=b1873482056030d0</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ddac65267477c40</t>
+          <t>https://www.indeed.com/viewjob?jk=ab22c7230af34e68</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e425667f20dcb7e</t>
+          <t>https://www.indeed.com/viewjob?jk=677be9646b0e06df</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1873482056030d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5e09a480919567</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab22c7230af34e68</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1bd277622288c0</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677be9646b0e06df</t>
+          <t>https://www.indeed.com/viewjob?jk=42a71d4cd495130b</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5e09a480919567</t>
+          <t>https://www.indeed.com/viewjob?jk=a52685267df3f959</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1bd277622288c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8fcc937a8b5e2489</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42a71d4cd495130b</t>
+          <t>https://www.indeed.com/viewjob?jk=d5ff1ae9ce8cebc9</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a52685267df3f959</t>
+          <t>https://www.indeed.com/viewjob?jk=caeae51b9c1b0f4a</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fcc937a8b5e2489</t>
+          <t>https://www.indeed.com/viewjob?jk=cdd2ae13e28a4887</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5ff1ae9ce8cebc9</t>
+          <t>https://www.indeed.com/viewjob?jk=06b3d09e86b123a8</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caeae51b9c1b0f4a</t>
+          <t>https://www.indeed.com/viewjob?jk=036b19c06fa11eda</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdd2ae13e28a4887</t>
+          <t>https://www.indeed.com/viewjob?jk=c11d63f000f42ba2</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b3d09e86b123a8</t>
+          <t>https://www.indeed.com/viewjob?jk=60e096ff0af09e5a</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=036b19c06fa11eda</t>
+          <t>https://www.indeed.com/viewjob?jk=5b043df0a94d01e0</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11d63f000f42ba2</t>
+          <t>https://www.indeed.com/viewjob?jk=4ebef8251dce5834</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e096ff0af09e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=59559b19a431de6c</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b043df0a94d01e0</t>
+          <t>https://www.indeed.com/viewjob?jk=18319f312711ee31</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ebef8251dce5834</t>
+          <t>https://www.indeed.com/viewjob?jk=e807d665db859229</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59559b19a431de6c</t>
+          <t>https://www.indeed.com/viewjob?jk=98a283e17753436e</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18319f312711ee31</t>
+          <t>https://www.indeed.com/viewjob?jk=f5c04a5eeae8858a</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e807d665db859229</t>
+          <t>https://www.indeed.com/viewjob?jk=04a2f6320142a662</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a283e17753436e</t>
+          <t>https://www.indeed.com/viewjob?jk=ba86b9b1e8a2c34b</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5c04a5eeae8858a</t>
+          <t>https://www.indeed.com/viewjob?jk=b8109c00824ee19e</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a2f6320142a662</t>
+          <t>https://www.indeed.com/viewjob?jk=0807f3685e925ebe</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba86b9b1e8a2c34b</t>
+          <t>https://www.indeed.com/viewjob?jk=abcd4343cd691b21</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8109c00824ee19e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc21abcfcbae5841</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0807f3685e925ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5172ad7fba06cf</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abcd4343cd691b21</t>
+          <t>https://www.indeed.com/viewjob?jk=95ccbb7fea6307b3</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc21abcfcbae5841</t>
+          <t>https://www.indeed.com/viewjob?jk=54ccb8a0b4e4366c</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3050,111 +3050,6 @@
         </is>
       </c>
       <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5172ad7fba06cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95ccbb7fea6307b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54ccb8a0b4e4366c</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=20da8d36ff151411</t>
         </is>

--- a/results/job_matches_2026-06-07.xlsx
+++ b/results/job_matches_2026-06-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Confluent Kafka Architect</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NSV IT SOLUTIONS</t>
+          <t>ATVIO Biotech</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3731032ae0f7a545</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac69009cfd6f44c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ATVIO Biotech</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac69009cfd6f44c</t>
+          <t>https://www.indeed.com/viewjob?jk=10e4d2d78aad0fb7</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e4d2d78aad0fb7</t>
+          <t>https://www.indeed.com/viewjob?jk=08dac6e8a6a35c88</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08dac6e8a6a35c88</t>
+          <t>https://www.indeed.com/viewjob?jk=fd370855fc5dbc9a</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd370855fc5dbc9a</t>
+          <t>https://www.indeed.com/viewjob?jk=d784be9eb68c3d91</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d784be9eb68c3d91</t>
+          <t>https://www.indeed.com/viewjob?jk=9da17c48b0c22ee4</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da17c48b0c22ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=49bd1e8c944ff980</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49bd1e8c944ff980</t>
+          <t>https://www.indeed.com/viewjob?jk=62cd9c61bbe2ba9a</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62cd9c61bbe2ba9a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e945058b2aeb81e</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e945058b2aeb81e</t>
+          <t>https://www.indeed.com/viewjob?jk=71e2a2a565e81c13</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e2a2a565e81c13</t>
+          <t>https://www.indeed.com/viewjob?jk=e4c2922604286744</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4c2922604286744</t>
+          <t>https://www.indeed.com/viewjob?jk=0eda203594437eb0</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eda203594437eb0</t>
+          <t>https://www.indeed.com/viewjob?jk=c7da71f5c4c140fd</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7da71f5c4c140fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c7e717cdb8e459ed</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e717cdb8e459ed</t>
+          <t>https://www.indeed.com/viewjob?jk=783563088e4850d3</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783563088e4850d3</t>
+          <t>https://www.indeed.com/viewjob?jk=caa727dc99a46aef</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa727dc99a46aef</t>
+          <t>https://www.indeed.com/viewjob?jk=8615c522efc71334</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8615c522efc71334</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6ae33243c395f5</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6ae33243c395f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b2caf8633eb99f5e</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2caf8633eb99f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=37c812e3f35b5835</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37c812e3f35b5835</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef92fef0e7ac2af</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef92fef0e7ac2af</t>
+          <t>https://www.indeed.com/viewjob?jk=82611021e50403b1</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82611021e50403b1</t>
+          <t>https://www.indeed.com/viewjob?jk=3964af1e193d6df3</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3964af1e193d6df3</t>
+          <t>https://www.indeed.com/viewjob?jk=57945f07d8dd1359</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57945f07d8dd1359</t>
+          <t>https://www.indeed.com/viewjob?jk=764072f6ce811075</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=764072f6ce811075</t>
+          <t>https://www.indeed.com/viewjob?jk=1b3b589ca8a6e80f</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b3b589ca8a6e80f</t>
+          <t>https://www.indeed.com/viewjob?jk=24650c3c8a602a7e</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24650c3c8a602a7e</t>
+          <t>https://www.indeed.com/viewjob?jk=03bea43e652f03fd</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03bea43e652f03fd</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb4026df23eb97b</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb4026df23eb97b</t>
+          <t>https://www.indeed.com/viewjob?jk=c93475e7d040c153</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c93475e7d040c153</t>
+          <t>https://www.indeed.com/viewjob?jk=456f8fa32939f19b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Senior AI Data Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Modine Manufacturing Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=456f8fa32939f19b</t>
+          <t>https://www.indeed.com/viewjob?jk=05d964f0d99760fd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior AI Data Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Modine Manufacturing Company</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,87 +1606,87 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d964f0d99760fd</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1fdc7b0acc6f95</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1fdc7b0acc6f95</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfb9a55bfdcda15</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Business Services Developer (Business Services Analyst)</t>
+          <t>Senior Product Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>County of Orange</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab95d16515240126</t>
+          <t>https://www.indeed.com/viewjob?jk=1c661fd3d1a35149</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfb9a55bfdcda15</t>
+          <t>https://www.indeed.com/viewjob?jk=3af5dbc4a7642e17</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c661fd3d1a35149</t>
+          <t>https://www.indeed.com/viewjob?jk=a05cc00f3398fb9e</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af5dbc4a7642e17</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb07a25aaeb4be3</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05cc00f3398fb9e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ddac65267477c40</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb07a25aaeb4be3</t>
+          <t>https://www.indeed.com/viewjob?jk=2e425667f20dcb7e</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ddac65267477c40</t>
+          <t>https://www.indeed.com/viewjob?jk=b1873482056030d0</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e425667f20dcb7e</t>
+          <t>https://www.indeed.com/viewjob?jk=ab22c7230af34e68</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1873482056030d0</t>
+          <t>https://www.indeed.com/viewjob?jk=677be9646b0e06df</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab22c7230af34e68</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5e09a480919567</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677be9646b0e06df</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1bd277622288c0</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5e09a480919567</t>
+          <t>https://www.indeed.com/viewjob?jk=42a71d4cd495130b</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1bd277622288c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a52685267df3f959</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42a71d4cd495130b</t>
+          <t>https://www.indeed.com/viewjob?jk=8fcc937a8b5e2489</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a52685267df3f959</t>
+          <t>https://www.indeed.com/viewjob?jk=d5ff1ae9ce8cebc9</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fcc937a8b5e2489</t>
+          <t>https://www.indeed.com/viewjob?jk=caeae51b9c1b0f4a</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5ff1ae9ce8cebc9</t>
+          <t>https://www.indeed.com/viewjob?jk=cdd2ae13e28a4887</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caeae51b9c1b0f4a</t>
+          <t>https://www.indeed.com/viewjob?jk=06b3d09e86b123a8</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdd2ae13e28a4887</t>
+          <t>https://www.indeed.com/viewjob?jk=036b19c06fa11eda</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b3d09e86b123a8</t>
+          <t>https://www.indeed.com/viewjob?jk=c11d63f000f42ba2</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=036b19c06fa11eda</t>
+          <t>https://www.indeed.com/viewjob?jk=60e096ff0af09e5a</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c11d63f000f42ba2</t>
+          <t>https://www.indeed.com/viewjob?jk=5b043df0a94d01e0</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e096ff0af09e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=4ebef8251dce5834</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b043df0a94d01e0</t>
+          <t>https://www.indeed.com/viewjob?jk=59559b19a431de6c</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ebef8251dce5834</t>
+          <t>https://www.indeed.com/viewjob?jk=18319f312711ee31</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59559b19a431de6c</t>
+          <t>https://www.indeed.com/viewjob?jk=e807d665db859229</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18319f312711ee31</t>
+          <t>https://www.indeed.com/viewjob?jk=98a283e17753436e</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e807d665db859229</t>
+          <t>https://www.indeed.com/viewjob?jk=f5c04a5eeae8858a</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98a283e17753436e</t>
+          <t>https://www.indeed.com/viewjob?jk=04a2f6320142a662</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5c04a5eeae8858a</t>
+          <t>https://www.indeed.com/viewjob?jk=ba86b9b1e8a2c34b</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a2f6320142a662</t>
+          <t>https://www.indeed.com/viewjob?jk=b8109c00824ee19e</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba86b9b1e8a2c34b</t>
+          <t>https://www.indeed.com/viewjob?jk=0807f3685e925ebe</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8109c00824ee19e</t>
+          <t>https://www.indeed.com/viewjob?jk=abcd4343cd691b21</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0807f3685e925ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=bc21abcfcbae5841</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abcd4343cd691b21</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5172ad7fba06cf</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc21abcfcbae5841</t>
+          <t>https://www.indeed.com/viewjob?jk=95ccbb7fea6307b3</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5172ad7fba06cf</t>
+          <t>https://www.indeed.com/viewjob?jk=54ccb8a0b4e4366c</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2980,76 +2980,6 @@
         </is>
       </c>
       <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95ccbb7fea6307b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54ccb8a0b4e4366c</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Product Architect</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Scala, NoSQL, AKS, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=20da8d36ff151411</t>
         </is>
